--- a/data/trans_orig/P78_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P78_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona sustentadora principal trabaja actualmente en 2023</t>
+          <t>Población según si la persona sustentadora principal trabaja actualmente en 2023 (tasa de respuesta: 99,42%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>135873</t>
+          <t>136296</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>151268</t>
+          <t>151041</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>151100</t>
+          <t>149130</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>187352</t>
+          <t>186395</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>292452</t>
+          <t>292694</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>339806</t>
+          <t>337922</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,36%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8699</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24094</t>
+          <t>23671</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>310645</t>
+          <t>311602</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>346897</t>
+          <t>348867</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>318159</t>
+          <t>320043</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>365513</t>
+          <t>365271</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,52%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1571778</t>
+          <t>1573910</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1645563</t>
+          <t>1649138</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>977650</t>
+          <t>925086</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1556050</t>
+          <t>1553148</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2417704</t>
+          <t>2414810</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3187371</t>
+          <t>3191443</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>90,04%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>64104</t>
+          <t>60529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>137889</t>
+          <t>135757</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>278750</t>
+          <t>281652</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>857150</t>
+          <t>909714</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>357095</t>
+          <t>353023</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1126762</t>
+          <t>1129656</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,87%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>465991</t>
+          <t>468107</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>489077</t>
+          <t>489949</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>493145</t>
+          <t>493650</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>513193</t>
+          <t>514196</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>969346</t>
+          <t>971296</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>998556</t>
+          <t>999429</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>6386</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30344</t>
+          <t>28228</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20185</t>
+          <t>19182</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40233</t>
+          <t>39728</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31157</t>
+          <t>30284</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>60367</t>
+          <t>58417</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2195245</t>
+          <t>2199852</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2275580</t>
+          <t>2278966</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1625260</t>
+          <t>1620881</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2211726</t>
+          <t>2215524</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3607236</t>
+          <t>3651584</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4490354</t>
+          <t>4488374</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,78%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90389</t>
+          <t>87003</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>170724</t>
+          <t>166117</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>654448</t>
+          <t>650650</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1240914</t>
+          <t>1245293</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>741789</t>
+          <t>743769</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1624907</t>
+          <t>1580559</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P78_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P78_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>144821</t>
+          <t>177978</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>136296</t>
+          <t>169219</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>151041</t>
+          <t>184781</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>168668</t>
+          <t>183231</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>149130</t>
+          <t>167017</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>186395</t>
+          <t>200713</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>313489</t>
+          <t>361209</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>292694</t>
+          <t>338089</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>337922</t>
+          <t>385196</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>52,62%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15146</t>
+          <t>15263</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>8460</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23671</t>
+          <t>24022</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>329329</t>
+          <t>355594</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>311602</t>
+          <t>338112</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>348867</t>
+          <t>371808</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>344476</t>
+          <t>370857</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>320043</t>
+          <t>346870</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>365271</t>
+          <t>393977</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>53,82%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>159967</t>
+          <t>193241</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>159967</t>
+          <t>193241</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>159967</t>
+          <t>193241</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>497997</t>
+          <t>538825</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>497997</t>
+          <t>538825</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>497997</t>
+          <t>538825</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>657965</t>
+          <t>732066</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>657965</t>
+          <t>732066</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>657965</t>
+          <t>732066</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1611768</t>
+          <t>1502883</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1573910</t>
+          <t>1475435</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1649138</t>
+          <t>1527060</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1368876</t>
+          <t>1444974</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>925086</t>
+          <t>1415916</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1553148</t>
+          <t>1472205</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2980643</t>
+          <t>2947856</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2414810</t>
+          <t>2903531</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3191443</t>
+          <t>2981220</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,76%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>97899</t>
+          <t>96146</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60529</t>
+          <t>71969</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>135757</t>
+          <t>123594</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>465924</t>
+          <t>277294</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>281652</t>
+          <t>250063</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>909714</t>
+          <t>306352</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>563823</t>
+          <t>373440</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>353023</t>
+          <t>340076</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1129656</t>
+          <t>417765</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1709667</t>
+          <t>1599029</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1709667</t>
+          <t>1599029</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1709667</t>
+          <t>1599029</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1834800</t>
+          <t>1722268</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1834800</t>
+          <t>1722268</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1834800</t>
+          <t>1722268</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3544466</t>
+          <t>3321296</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3544466</t>
+          <t>3321296</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3544466</t>
+          <t>3321296</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>481348</t>
+          <t>529858</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>468107</t>
+          <t>515440</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>489949</t>
+          <t>537254</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>505042</t>
+          <t>557032</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>493650</t>
+          <t>545040</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>514196</t>
+          <t>565650</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>986390</t>
+          <t>1086890</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>971296</t>
+          <t>1070429</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>999429</t>
+          <t>1100166</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14987</t>
+          <t>15111</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>7715</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28228</t>
+          <t>29529</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28336</t>
+          <t>29548</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19182</t>
+          <t>20930</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39728</t>
+          <t>41540</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>43323</t>
+          <t>44659</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30284</t>
+          <t>31383</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>58417</t>
+          <t>61120</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>496335</t>
+          <t>544969</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>496335</t>
+          <t>544969</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>496335</t>
+          <t>544969</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>533378</t>
+          <t>586580</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>533378</t>
+          <t>586580</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>533378</t>
+          <t>586580</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1029713</t>
+          <t>1131549</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1029713</t>
+          <t>1131549</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1029713</t>
+          <t>1131549</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,17 +1754,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2237936</t>
+          <t>2210719</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2199852</t>
+          <t>2175914</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2278966</t>
+          <t>2237466</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2042585</t>
+          <t>2185237</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1620881</t>
+          <t>2140088</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2215524</t>
+          <t>2222047</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4280521</t>
+          <t>4395955</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3651584</t>
+          <t>4338869</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4488374</t>
+          <t>4435771</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,55%</t>
         </is>
       </c>
     </row>
@@ -1867,17 +1867,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>128033</t>
+          <t>126520</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87003</t>
+          <t>99773</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>166117</t>
+          <t>161325</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>823589</t>
+          <t>662436</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>650650</t>
+          <t>625626</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1245293</t>
+          <t>707585</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>951622</t>
+          <t>788956</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>743769</t>
+          <t>749140</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1580559</t>
+          <t>846042</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2365969</t>
+          <t>2337239</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2365969</t>
+          <t>2337239</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2365969</t>
+          <t>2337239</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2866174</t>
+          <t>2847673</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2866174</t>
+          <t>2847673</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2866174</t>
+          <t>2847673</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>5232143</t>
+          <t>5184911</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>5232143</t>
+          <t>5184911</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5232143</t>
+          <t>5184911</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
